--- a/Shiny/Datos limpios/pricing_semanal_total_2025.xlsx
+++ b/Shiny/Datos limpios/pricing_semanal_total_2025.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="20.7109375" style="2" customWidth="1"/>
@@ -1591,10 +1591,10 @@
         <v>19838.64</v>
       </c>
       <c r="I38">
-        <v>368355.97</v>
+        <v>368215.29</v>
       </c>
       <c r="J38">
-        <v>1994882.79</v>
+        <v>1994742.11</v>
       </c>
     </row>
     <row r="39">
@@ -1623,10 +1623,10 @@
         <v>28907.18</v>
       </c>
       <c r="I39">
-        <v>520891.25</v>
+        <v>520857.33</v>
       </c>
       <c r="J39">
-        <v>1972655.94</v>
+        <v>1972622.02</v>
       </c>
     </row>
     <row r="40">
@@ -1649,16 +1649,16 @@
         <v>639784.35</v>
       </c>
       <c r="G40">
-        <v>4617338.97</v>
+        <v>4615992.54</v>
       </c>
       <c r="H40">
         <v>16898.25</v>
       </c>
       <c r="I40">
-        <v>594174.1399999999</v>
+        <v>592986.4099999999</v>
       </c>
       <c r="J40">
-        <v>6251514.619999999</v>
+        <v>6248980.46</v>
       </c>
     </row>
     <row r="41">
@@ -1681,16 +1681,16 @@
         <v>395206.84</v>
       </c>
       <c r="G41">
-        <v>2298314.3</v>
+        <v>2298163.85</v>
       </c>
       <c r="H41">
         <v>35504.45</v>
       </c>
       <c r="I41">
-        <v>335583.54</v>
+        <v>335171.96</v>
       </c>
       <c r="J41">
-        <v>3242966.96</v>
+        <v>3242404.93</v>
       </c>
     </row>
     <row r="42">
@@ -1713,16 +1713,16 @@
         <v>304012.16</v>
       </c>
       <c r="G42">
-        <v>1169573.25</v>
+        <v>1169453.25</v>
       </c>
       <c r="H42">
         <v>5781.29</v>
       </c>
       <c r="I42">
-        <v>489653.0699999999</v>
+        <v>489497.7999999999</v>
       </c>
       <c r="J42">
-        <v>2082240.08</v>
+        <v>2081964.81</v>
       </c>
     </row>
     <row r="43">
@@ -1748,13 +1748,13 @@
         <v>601842.1599999999</v>
       </c>
       <c r="H43">
-        <v>22638.86</v>
+        <v>21638.86</v>
       </c>
       <c r="I43">
-        <v>773596.66</v>
+        <v>773300.1</v>
       </c>
       <c r="J43">
-        <v>1998562.06</v>
+        <v>1997265.5</v>
       </c>
     </row>
     <row r="44">
@@ -1800,25 +1800,121 @@
         <v>45957</v>
       </c>
       <c r="D45">
-        <v>7950</v>
+        <v>102278.83</v>
       </c>
       <c r="E45">
-        <v>950</v>
+        <v>59661.56</v>
       </c>
       <c r="F45">
-        <v>1510</v>
+        <v>554294.73</v>
       </c>
       <c r="G45">
-        <v>2677.84</v>
+        <v>353649.61</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>13062</v>
       </c>
       <c r="I45">
-        <v>960</v>
+        <v>399832.23</v>
       </c>
       <c r="J45">
-        <v>14047.84</v>
+        <v>1482778.96</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>2025</v>
+      </c>
+      <c r="B46">
+        <v>45</v>
+      </c>
+      <c r="C46" s="2">
+        <v>45964</v>
+      </c>
+      <c r="D46">
+        <v>124568.03</v>
+      </c>
+      <c r="E46">
+        <v>65910.09999999999</v>
+      </c>
+      <c r="F46">
+        <v>874205.9600000001</v>
+      </c>
+      <c r="G46">
+        <v>473276.52</v>
+      </c>
+      <c r="H46">
+        <v>13193.05</v>
+      </c>
+      <c r="I46">
+        <v>405527.27</v>
+      </c>
+      <c r="J46">
+        <v>1956680.93</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>2025</v>
+      </c>
+      <c r="B47">
+        <v>46</v>
+      </c>
+      <c r="C47" s="2">
+        <v>45971</v>
+      </c>
+      <c r="D47">
+        <v>77703.97</v>
+      </c>
+      <c r="E47">
+        <v>56736.91</v>
+      </c>
+      <c r="F47">
+        <v>1014195.06</v>
+      </c>
+      <c r="G47">
+        <v>333538.6299999999</v>
+      </c>
+      <c r="H47">
+        <v>7740.780000000001</v>
+      </c>
+      <c r="I47">
+        <v>600952.0399999999</v>
+      </c>
+      <c r="J47">
+        <v>2090867.39</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>2025</v>
+      </c>
+      <c r="B48">
+        <v>47</v>
+      </c>
+      <c r="C48" s="2">
+        <v>45978</v>
+      </c>
+      <c r="D48">
+        <v>125853.85</v>
+      </c>
+      <c r="E48">
+        <v>43395.28</v>
+      </c>
+      <c r="F48">
+        <v>384460.97</v>
+      </c>
+      <c r="G48">
+        <v>351428.9399999999</v>
+      </c>
+      <c r="H48">
+        <v>3714.14</v>
+      </c>
+      <c r="I48">
+        <v>487343.15</v>
+      </c>
+      <c r="J48">
+        <v>1396196.33</v>
       </c>
     </row>
   </sheetData>
